--- a/data/source/2026-08/1С-Обороты-счета-91-август-2026.xlsx
+++ b/data/source/2026-08/1С-Обороты-счета-91-август-2026.xlsx
@@ -544,10 +544,10 @@
       </c>
       <c r="C9" s="18" t="e"/>
       <c r="D9" s="17" t="n">
-        <v>514768.62</v>
+        <v>518510.87</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>137448.82</v>
+        <v>141191.07</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>373487.16</v>
@@ -562,7 +562,7 @@
         <v>396337.24</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>137011.72</v>
+        <v>140753.97</v>
       </c>
       <c r="K9" s="18" t="e"/>
     </row>
@@ -575,10 +575,10 @@
         <v>97060.85</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>37239</v>
+        <v>40981.25</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>37239</v>
+        <v>40981.25</v>
       </c>
       <c r="F10" s="22" t="e"/>
       <c r="G10" s="22" t="e"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="J10" s="20" t="e"/>
       <c r="K10" s="21" t="n">
-        <v>90339.25</v>
+        <v>86597</v>
       </c>
     </row>
     <row r="11" ht="50" customHeight="true" outlineLevel="2">
@@ -619,10 +619,10 @@
       <c r="B12" s="24" t="e"/>
       <c r="C12" s="24" t="e"/>
       <c r="D12" s="26" t="n">
-        <v>37239</v>
+        <v>40981.25</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>37239</v>
+        <v>40981.25</v>
       </c>
       <c r="F12" s="25" t="e"/>
       <c r="G12" s="25" t="e"/>
@@ -806,10 +806,10 @@
       </c>
       <c r="C21" s="29" t="e"/>
       <c r="D21" s="28" t="n">
-        <v>514768.62</v>
+        <v>518510.87</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>137448.82</v>
+        <v>141191.07</v>
       </c>
       <c r="F21" s="28" t="n">
         <v>373487.16</v>
@@ -824,7 +824,7 @@
         <v>396337.24</v>
       </c>
       <c r="J21" s="28" t="n">
-        <v>137011.72</v>
+        <v>140753.97</v>
       </c>
       <c r="K21" s="29" t="e"/>
     </row>
